--- a/content/Question Bank/MCQ/Unit 10 - Modules and Packages/Unit 10 - Modules and Packages - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 10 - Modules and Packages/Unit 10 - Modules and Packages - MCQ.xlsx
@@ -907,7 +907,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Why is it important to know that `random.randint(1, 6)` includes both endpoints, unlike `range()`?</t>
+          <t>A board-game app rolls a virtual die using `random.randint(1, 6)` and a developer wants to avoid an off-by-one bug when validating the result range. Why is it important to know that `random.randint(1, 6)` includes both endpoints, unlike `range()`?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -985,7 +985,8 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>```python
+          <t>A travel-booking app needs to show a user how many days remain before their trip, so it runs:
+```python
 trip_date = datetime.date(2026, 8, 15)
 today = datetime.date(2026, 7, 1)
 days_left = trip_date - today
@@ -1069,9 +1070,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pip freeze &gt; `requirements.txt`
+          <t>A developer handing off a machine-learning project to a teammate on another computer runs these two commands to make sure the environment matches exactly:
+```
+pip freeze &gt; requirements.txt
 ...
-pip install -r `requirements.txt`
+pip install -r requirements.txt
+```
 What do these two commands accomplish together, run on two different machines?</t>
         </is>
       </c>
@@ -1150,7 +1154,8 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>```python
+          <t>A hotel booking system runs into a naming clash after a developer imports two similarly named helper functions:
+```python
 from billing import format
 from receipts import format
 print(format(1500))
@@ -1490,7 +1495,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>What is a Python module, in the simplest correct terms?</t>
+          <t>A new intern on a coding team keeps hearing the word "module" and wants a plain definition before writing any code. What is a Python module, in the simplest correct terms?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1568,7 +1573,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>What problem do modules solve that plain functions inside one file cannot solve well?</t>
+          <t>A team's chatbot script has grown to 2,000 lines with every helper function crammed into one file, making it hard to navigate. What problem do modules solve that plain functions inside one file cannot solve well?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1646,7 +1651,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which statement correctly imports the entire math module?</t>
+          <t>A weather-alert script needs access to every function in the math module to calculate wind-chill formulas. Which statement correctly imports the entire math module?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1724,7 +1729,8 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>```python
+          <t>A fitness app needs to compute a user's daily calorie target using square roots and a rounded-up step count, so a developer runs this code:
+```python
 from math import sqrt, pi
 print(sqrt(16))
 print(pi)
@@ -1807,7 +1813,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A bug is found inside a function that was copy-pasted into five different scripts. How would organizing that function into a shared module have helped?</t>
+          <t>A bug in a shipping-cost calculator was found inside a function that had been copy-pasted into five different delivery scripts across the company. How would organizing that function into a shared module have helped?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1885,7 +1891,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>What is the Python standard library?</t>
+          <t>A new developer joins a logistics company and is told to "just use the standard library" for date handling instead of installing anything. What is the Python standard library?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1963,7 +1969,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Why does code typically write `math.sqrt(16)` instead of just `sqrt(16)` after import math?</t>
+          <t>A student building a dice-rolling game imports the math module and wants to know the convention for calling its functions. Why does code typically write `math.sqrt(16)` instead of just `sqrt(16)` after import math?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2041,7 +2047,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>What does import math as m accomplish?</t>
+          <t>A data analyst wants to shorten repeated references to the math module throughout a stats script. What does import math as m accomplish?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2119,7 +2125,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A script has `split_cost()`, `add_service_charge()`, `format_receipt()`, `days_until_trip()`, and `random_room_assignment()`. Which functions most naturally belong together in one module?</t>
+          <t>A restaurant billing app has grown to include `split_cost()`, `add_service_charge()`, `format_receipt()`, `days_until_trip()`, and `random_room_assignment()` all in one file. Which functions most naturally belong together in one module?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2197,7 +2203,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>What is required to turn a Python file into a usable module?</t>
+          <t>A student has written a helper file called `discount_calc.py` and wants other scripts in the same folder to be able to import it. What is required to turn a Python file into a usable module?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2376,7 +2382,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Why does using import billing and import receipts (instead of from billing import format and from receipts import format) avoid a naming collision when both modules define format?</t>
+          <t>A ticket-booking platform's codebase avoids a naming clash by importing two modules that both define a function called format, using import billing and import receipts instead of pulling the function names directly. Why does using import billing and import receipts (instead of from billing import format and from receipts import format) avoid a naming collision when both modules define format?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2454,7 +2460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which of these is the most appropriate name for a module file containing receipt formatting functions?</t>
+          <t>A developer is organizing a hotel booking system's codebase and needs a file to hold receipt-formatting functions. Which of these is the most appropriate name for a module file containing receipt formatting functions?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2532,7 +2538,8 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>```python
+          <t>A physics tutoring app renames an imported function for clarity in its worksheet-generator script:
+```python
 from math import sqrt as square_root
 print(square_root(36))
 ```
@@ -2848,7 +2855,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>What is the difference between running `billing.py` directly and importing it from `main.py`?</t>
+          <t>A junior developer is confused after seeing `billing.py` behave differently depending on how it's used in a payroll project. What is the difference between running `billing.py` directly and importing it from `main.py`?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2926,7 +2933,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>What is the minimum required content of `__init__`.py for a folder to function as a package?</t>
+          <t>A team is setting up a new package called `tools` for their inventory system and wants the folder to be recognized as an importable package. What is the minimum required content of `__init__`.py for a folder to function as a package?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3004,7 +3011,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>tools/`__init__`.py contains: from .billing import split_cost
+          <t>In an e-commerce project's `tools` package, the file structure includes `tools/__init__`.py containing: from .billing import split_cost
 What does this allow `main.py` to do?</t>
         </is>
       </c>
@@ -3083,7 +3090,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>What two things make a folder a Python package?</t>
+          <t>A developer organizing a delivery-tracking project wants to turn a folder called `utils` into a proper Python package. What two things make a folder a Python package?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3262,7 +3269,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>What is the core job of pip install package_name, and what does PyPI provide?</t>
+          <t>A developer building a weather app wants to install a third-party library for fetching forecasts and needs to understand where it will come from. What is the core job of pip install package_name, and what does PyPI provide?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3340,7 +3347,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Why does import math work with no install step, while import requests requires pip install requests first?</t>
+          <t>A developer setting up a new expense-tracking app notices that import math just works immediately, but import requests fails until a separate install step runs first. Why does import math work with no install step, while import requests requires pip install requests first?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3418,7 +3425,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Why can repeatedly running plain pip install commands directly on a machine, without any isolation, become risky across multiple projects?</t>
+          <t>A freelance developer juggling several client projects on one laptop keeps running plain pip install commands directly on the machine with no isolation between projects. Why can this become risky across multiple projects?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3574,7 +3581,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Inside tools/`__init__`.py, what does the leading dot in from .billing import split_cost mean?</t>
+          <t>Inside an online bookstore project's `tools/__init__`.py file, a developer sees a relative import: from .billing import split_cost. What does the leading dot in from .billing import split_cost mean?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3652,7 +3659,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which command shows version and dependency details about one specific installed package?</t>
+          <t>A developer maintaining a ticket-booking system needs to check the exact version and dependencies of one already-installed library before upgrading it. Which command shows version and dependency details about one specific installed package?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3730,7 +3737,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>What is the relationship between uv and the venv plus pip workflow?</t>
+          <t>A student switching teams at a startup hears a coworker mention using "uv" instead of the usual venv-and-pip routine for their social media analytics project. What is the relationship between uv and the venv plus pip workflow?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3808,9 +3815,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>uv venv
+          <t>Setting up a new microservice for a food-delivery app, a developer runs the following in sequence:
+```
+uv venv
 uv add requests
 uv run `my_script.py`
+```
 What does this three-line sequence accomplish?</t>
         </is>
       </c>
@@ -3889,7 +3899,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What is the correct sequence to create and then activate a virtual environment on macOS/Linux?</t>
+          <t>A student setting up their first virtual environment for a school project on macOS wants to get the command order right before installing any packages. What is the correct sequence to create and then activate a virtual environment on macOS/Linux?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">

--- a/content/Question Bank/MCQ/Unit 10 - Modules and Packages/Unit 10 - Modules and Packages - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 10 - Modules and Packages/Unit 10 - Modules and Packages - MCQ.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Python - MCQ - 10.1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Python - MCQ - 10.2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Python - MCQ - 10.3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Python - MCQ - 10.4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 10.1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 10.2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 10.3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 10.4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -643,26 +643,26 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>The current working directory's path only</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Every file and folder in the current directory</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>The total disk space available</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>A random file from the current directory</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Every file and folder in the current directory</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>The current working directory's path only</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -721,22 +721,22 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>File reading and writing utilities for working with data</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Date and time calculation utilities for scheduling tasks</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Mathematical operations beyond basic arithmetic, like sqrt and ceil</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>Random number generation utilities for simulations and games</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Date and time calculation utilities for scheduling tasks</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Mathematical operations beyond basic arithmetic, like sqrt and ceil</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>File reading and writing utilities for working with data</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -799,26 +799,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>It deletes one of the two conflicting projects automatically</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>It prevents either project from installing any packages at all</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>It merges both required versions into a single compatible one</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>It gives each project its own isolated set of installed packages</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>It deletes one of the two conflicting projects automatically</t>
-        </is>
-      </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -877,22 +877,22 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>pandas</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>numpy</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>requests</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>random</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>numpy</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>pandas</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -955,12 +955,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>`range()` is technically always inclusive too, so there is genuinely no difference</t>
+          <t>Mixing up the inclusive behavior of randint with range's exclusive behavior risks an off-by-one mistake</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Mixing up the inclusive behavior of randint with range's exclusive behavior risks an off-by-one mistake</t>
+          <t>It genuinely does not matter at all, both behave in an identical way</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -970,11 +970,11 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>It genuinely does not matter at all, both behave in an identical way</t>
+          <t>`range()` is technically always inclusive too, so there is genuinely no real difference here at all</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1040,26 +1040,26 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>'45 days', as a string</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>A `TypeError`, since dates cannot be subtracted</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>A `TypeError`, since dates cannot be subtracted</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>'45 days', as a string</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>They only work if both machines have the exact same operating system installed beforehand</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>They install Python itself on a new machine</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>They only work if both machines have the exact same operating system installed beforehand</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1213,21 +1213,21 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t>Python raises an `ImportError` immediately</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>The second import silently overwrites the first, with no warning</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>Only the first import's format is ever usable</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Python raises an `ImportError` immediately</t>
-        </is>
-      </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
+          <t>It would not help at all; flat folders scale just as well as packages always would</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>Packages are required by Python once a project exceeds ten files</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>Packages technically make individual modules run measurably faster</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>It would not help; flat folders scale just as well as packages always</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1364,14 +1364,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>It raises an `ImportError` because of the stray print call</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>The print statement runs every time the module is imported, anywhere</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>It raises an `ImportError` because of the stray print call</t>
-        </is>
-      </c>
       <c r="O11" t="inlineStr">
         <is>
           <t>The print statement only runs the first time the module is ever imported, system-wide</t>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1543,22 +1543,22 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>A built-in Python keyword</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Any .py file, with no extra syntax required</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>A special file type that needs a .mod extension</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>A folder containing an `__init__`.py file</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Any .py file, with no extra syntax required</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>A built-in Python keyword</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>A special file type that needs a .mod extension</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -1621,26 +1621,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>They let you organize logic across files and reuse it without copy-pasting</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>They technically make the code run faster completely automatically</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>They technically remove the entire need for functions altogether</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>They technically allow Python to skip all syntax checking entirely</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>They technically remove the entire need for functions altogether</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>They technically make the code run faster completely automatically</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>They let you organize logic across files and reuse it without copy-pasting</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1699,26 +1699,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>import math</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>from math</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>module math</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>import math</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>include math</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1783,26 +1783,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>4.0 then 3.141592653589793</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>16 then 3.14</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>An error, since sqrt and pi need a prefix</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>`math.sqrt(16)` then `math.pi`</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>An error, since sqrt and pi need a prefix</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>16 then 3.14</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>4.0 then 3.141592653589793</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1861,26 +1861,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>Modules automatically detect and fix bugs</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>It would only fix the bug in the first script that happens to import it</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>It would not help, since modules cannot contain functions</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>Fixing the bug once in the module fixes it everywhere the module is imported</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Modules automatically detect and fix bugs</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>It would only fix the bug in the first script that imports it</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>It would not help, since modules cannot contain functions</t>
-        </is>
-      </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -1944,21 +1944,21 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>The collection of modules that ships automatically with Python itself</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>A paid set of modules available only to premium subscribers</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>A list of every variable ever defined in a script</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>A paid set of modules available only to subscribers</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>The collection of modules that ships automatically with Python itself</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -2017,26 +2017,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>Because plain import is technically slower whenever there is no prefix</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Because sqrt technically cannot exist at all without a prefix in Python</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>Because the prefix keeps the imported name's origin clear and avoids naming clashes</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>Because Python technically requires a prefix on every single function call</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Because sqrt technically cannot exist at all without a prefix in Python</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Because plain import is technically slower whenever there is no prefix</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -2095,26 +2095,26 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>It creates a brand new copy of the math module</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>It deletes the original math module name</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>It imports only part of the math module</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>It renames the imported module locally to a chosen alias</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>It creates a brand new copy of the math module</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>It imports only part of the math module</t>
-        </is>
-      </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -2173,26 +2173,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>Only random_room_assignment, since it specifically and uniquely uses randomness</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>All five belong in exactly one module, regardless of purpose</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>split_cost, add_service_charge, and format_receipt, since they share a billing purpose</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>`None` of them at all, since modules technically cannot group functions</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>All five belong in exactly one module, regardless of purpose</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Only random_room_assignment, since it specifically uses randomness</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>split_cost, add_service_charge, and format_receipt, since they share a billing purpose</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -2251,22 +2251,22 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>Renaming the file extension to .mod</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Saving it as a .py file; no extra syntax is needed</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Adding a special 'module' keyword at the top of the file</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>Registering the file with PyPI first</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Saving it as a .py file; no extra syntax is needed</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Renaming the file extension to .mod</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Adding a special 'module' keyword at the top of the file</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -2435,21 +2435,21 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>Because plain import renames duplicate functions automatically</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>The module prefix keeps both format functions distinct and both usable</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Because plain import renames duplicate functions automatically</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>It does not avoid the collision at all</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -2508,17 +2508,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>RECEIPT-FORMATTER</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>`receipt_formatter.py`</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>`ReceiptFormatter.PY`</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>`receipt_formatter.py`</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>RECEIPT-FORMATTER</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2591,17 +2591,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>1296.0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>An error, since sqrt was renamed</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>36.0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>1296.0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>An error, since sqrt was renamed</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -2669,26 +2669,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>`random.randint` cannot generate numbers between 1 and 6</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>It needlessly reinvents tested functionality the standard library already provides</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>There is no downside, both approaches are equally good practice</t>
-        </is>
-      </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>There is no downside at all, both approaches are equally good practice</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>Custom loops always run faster than standard library functions</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>`random.randint` cannot generate numbers between 1 and 6</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2747,26 +2747,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>Because `billing.py` was registered in a system-wide config file</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Because Python searches the same folder as the importing script by default</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Because every Python file is globally importable from anywhere</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>Because `main.py` and `billing.py` must share the same first line of code</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Because every Python file is globally importable from anywhere</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Because `billing.py` was registered in a system-wide config file</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Because Python searches the same folder as the importing script by default</t>
-        </is>
-      </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -2835,12 +2835,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
+          <t>`tools.py.billing.split_cost()` called this way</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>import `tools.billing.split_cost` directly like this</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>`tools.py.billing.split_cost()` called this way</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -2903,26 +2903,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>Imported modules cannot define functions, only run scripts can</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>Importing never executes any code in the module at all</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Both execute the module's top-level code; only the entry point differs</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>Running a module directly disables all its function definitions</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Imported modules cannot define functions, only run scripts can</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Both execute the module's top-level code; only the entry point differs</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -2981,26 +2981,26 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>It can be completely empty; its presence alone marks the folder as a package</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>It technically must import the entire standard library at once</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>It technically must contain at least one class definition inside it</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>It can be completely empty; its presence alone marks the folder as a package</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>It technically must list every single module in the folder by name</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -3060,26 +3060,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>It technically deletes the billing module entirely from the package</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>`main.py` must now import `billing.py` as a separate top-level module</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Nothing changes at all; `__init__`.py code technically never actually runs</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>`main.py` can now write from tools import split_cost directly, skipping the billing name</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Nothing changes at all; `__init__`.py code technically never actually runs</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>It technically deletes the billing module entirely from the package</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>`main.py` must now import `billing.py` as a separate top-level module</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -3138,26 +3138,26 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>A folder of related modules plus an `__init__`.py file inside it</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>A folder that has been registered somewhere with pip</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>A folder that happens to be named exactly 'package'</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>Any folder that simply contains at least one .py file inside it</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>A folder that happens to be named exactly 'package'</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>A folder that has been registered somewhere with pip</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>A folder of related modules plus an `__init__`.py file inside it</t>
-        </is>
-      </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3317,26 +3317,26 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>It downloads and installs a package from PyPI</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>It deletes a package permanently from PyPI</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>It writes new Python syntax into the language itself</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>It only checks if a package exists, without installing it</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>It downloads and installs a package from PyPI</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>It writes new Python syntax into the language itself</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -3395,26 +3395,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>There is technically no real difference at all; both always require installation</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>math ships with Python itself, while requests is a third-party package from PyPI needing an explicit install</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>math technically requires installation too, but is simply pre-installed on all machines</t>
-        </is>
-      </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>There is technically no real difference at all; both always require installation</t>
+          <t>requests is technically actually already part of the standard library too</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>requests is technically actually already part of the standard library too</t>
+          <t>math technically requires installation too, but is simply pre-installed on every machine already</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -3473,26 +3473,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>It is technically never risky at all, since pip always keeps every single version side by side</t>
+          <t>pip technically refuses outright to install a second package once one is already installed</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>pip technically refuses outright to install a second package once one is already installed</t>
+          <t>It is technically never risky at all, since pip supposedly always keeps every single version side by side forever</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
+          <t>Global installs are technically automatically and fully isolated per project by default</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>A later install can silently change the version an earlier project depended on, since only one global version exists at a time</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Global installs are technically automatically and fully isolated per project by default</t>
-        </is>
-      </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -3551,26 +3551,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>It installs into the global Python environment instead of .venv, since activation never happened</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>It installs correctly into .venv every time, regardless of activation</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>It fails outright with a clear error, because no environment is currently active at all</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>It installs into both the global Python and .venv simultaneously</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>It fails outright with an error, because no environment is currently active</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>It installs into the global Python environment instead of .venv, since activation never happened</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3629,26 +3629,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>It means 'from the parent directory of the project'</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>It means 'from a module in this same package'</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>It is a typo and has no real meaning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>It means 'import this module twice'</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>It means 'from the parent directory of the project'</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>It means 'from a module in this same package'</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>It is a typo and has no real meaning</t>
-        </is>
-      </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -3707,26 +3707,26 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>pip list</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>pip uninstall package_name</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>pip show package_name</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>pip list</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>pip freeze</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>pip uninstall package_name</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -3785,26 +3785,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>uv technically only ever works for projects that never make use of pip at all</t>
+          <t>uv replaces Python itself and removes the need for pip syntax knowledge</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>uv performs the same core jobs as venv and pip, but executes them faster, with added conveniences</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>uv technically only ever works for projects that never make any use of pip at all, ever</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>uv is technically a fully paid, closed-source alternative to the venv tool</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>uv replaces Python itself and removes the need for pip syntax knowledge</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>uv performs the same core jobs as venv and pip, but executes them faster, with added conveniences</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>It technically only installs requests globally, ignoring environments entirely</t>
+          <t>It deletes any existing virtual environment before running the script</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>It deletes any existing virtual environment before running the script</t>
+          <t>It technically only installs requests globally, ignoring environments entirely every time</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
+          <t>pip install venv, followed then by venv start</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>venv create, followed then by venv run</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>pip install venv, followed then by venv start</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -4025,26 +4025,26 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>The new team should have manually guessed every package the project might need</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Nothing was missing; .venv should always be committed directly to version control</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Python should have installed the missing package automatically with no file needed</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>The developer never generated and shared a `requirements.txt` recording the exact dependencies</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>The new team should have manually guessed every package the project might need</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Nothing was missing; .venv should always be committed directly to version control</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Python should have installed the missing package automatically with no file needed</t>
-        </is>
-      </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/content/Question Bank/MCQ/Unit 10 - Modules and Packages/Unit 10 - Modules and Packages - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 10 - Modules and Packages/Unit 10 - Modules and Packages - MCQ.xlsx
@@ -2130,7 +2130,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>split_cost, add_service_charge, and format_receipt are all billing and receipt related, sharing a clear common purpose, while days_until_trip and random_room_assignment serve unrelated concerns and fit better elsewhere.</t>
+          <t>`split_cost`, `add_service_charge`, and `format_receipt` are all billing and receipt related, sharing a clear common purpose, while `days_until_trip` and `random_room_assignment` serve unrelated concerns and fit better elsewhere.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Only random_room_assignment, since it specifically and uniquely uses randomness</t>
+          <t>Only `random_room_assignment`, since it specifically and uniquely uses randomness</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>split_cost, add_service_charge, and format_receipt, since they share a billing purpose</t>
+          <t>`split_cost`, `add_service_charge`, and `format_receipt`, since they share a billing purpose</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Module names follow the same snake_case convention as variables and functions: lowercase words separated by underscores, descriptive of their contents, so `receipt_formatter.py` is appropriate while a vague name like `stuff.py` documents nothing.</t>
+          <t>Module names follow the same `snake_case` convention as variables and functions: lowercase words separated by underscores, descriptive of their contents, so `receipt_formatter.py` is appropriate while a vague name like `stuff.py` documents nothing.</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The alias renames sqrt to square_root for use in this script only; calling `square_root(36)` still runs math's sqrt function and returns 6.0.</t>
+          <t>The alias renames sqrt to `square_root` for use in this script only; calling `square_root(36)` still runs math's sqrt function and returns 6.0.</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -3011,13 +3011,13 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>In an e-commerce project's `tools` package, the file structure includes `tools/__init__`.py containing: from .billing import split_cost
+          <t>In an e-commerce project's `tools` package, the file structure includes `tools/__init__`.py containing: from .billing import `split_cost`
 What does this allow `main.py` to do?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>This re-export lets `main.py` write from tools import split_cost directly, without separately naming the billing module, since `__init__`.py code runs when the package itself is first imported and can expose inner names at the package level.</t>
+          <t>This re-export lets `main.py` write from tools import `split_cost` directly, without separately naming the billing module, since `__init__`.py code runs when the package itself is first imported and can expose inner names at the package level.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>`main.py` can now write from tools import split_cost directly, skipping the billing name</t>
+          <t>`main.py` can now write from tools import `split_cost` directly, skipping the billing name</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A developer building a weather app wants to install a third-party library for fetching forecasts and needs to understand where it will come from. What is the core job of pip install package_name, and what does PyPI provide?</t>
+          <t>A developer building a weather app wants to install a third-party library for fetching forecasts and needs to understand where it will come from. What is the core job of pip install `package_name`, and what does PyPI provide?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Inside an online bookstore project's `tools/__init__`.py file, a developer sees a relative import: from .billing import split_cost. What does the leading dot in from .billing import split_cost mean?</t>
+          <t>Inside an online bookstore project's `tools/__init__`.py file, a developer sees a relative import: from .billing import `split_cost`. What does the leading dot in from .billing import `split_cost` mean?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pip show package_name prints details about a single installed package, including its version, origin, and dependencies, while pip list simply enumerates every installed package without that detail.</t>
+          <t>pip show `package_name` prints details about a single installed package, including its version, origin, and dependencies, while pip list simply enumerates every installed package without that detail.</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>pip uninstall package_name</t>
+          <t>pip uninstall `package_name`</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>pip show package_name</t>
+          <t>pip show `package_name`</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">

--- a/content/Question Bank/MCQ/Unit 10 - Modules and Packages/Unit 10 - Modules and Packages - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 10 - Modules and Packages/Unit 10 - Modules and Packages - MCQ.xlsx
@@ -1243,7 +1243,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A dozen loose modules in one flat folder recreates the original 'one giant file' clutter problem one level up; grouping related modules into packages lets folders mirror the natural categories of the project and gives `__init__`.py a place to curate what is meant to be used from outside.</t>
+          <t>A dozen loose modules in one flat folder recreates the original 'one giant file' clutter problem one level up; grouping related modules into packages lets folders mirror the natural categories of the project and gives `__init__.py` a place to curate what is meant to be used from outside.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>`billing.py` contains a `print(split_cost(1000, 5))` statement directly at the top level, outside any function. What happens every time another script writes import billing?</t>
+          <t>`billing.py` contains a `print(split_cost(1000, 5))` statement directly at the top level, outside any function. What happens every time another script writes `import billing`?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A folder containing an `__init__`.py file</t>
+          <t>A folder containing an `__init__.py` file</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A team is setting up a new package called `tools` for their inventory system and wants the folder to be recognized as an importable package. What is the minimum required content of `__init__`.py for a folder to function as a package?</t>
+          <t>A team is setting up a new package called `tools` for their inventory system and wants the folder to be recognized as an importable package. What is the minimum required content of `__init__.py` for a folder to function as a package?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>`__init__`.py can be completely empty; its mere presence in the folder is sufficient to mark it as a package, with no required content inside it.</t>
+          <t>`__init__.py` can be completely empty; its mere presence in the folder is sufficient to mark it as a package, with no required content inside it.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -3011,13 +3011,13 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>In an e-commerce project's `tools` package, the file structure includes `tools/__init__`.py containing: from .billing import `split_cost`
+          <t>In an e-commerce project's `tools` package, the file structure includes `tools/__init__.py` containing: `from .billing import split_cost`
 What does this allow `main.py` to do?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>This re-export lets `main.py` write from tools import `split_cost` directly, without separately naming the billing module, since `__init__`.py code runs when the package itself is first imported and can expose inner names at the package level.</t>
+          <t>This re-export lets `main.py` write `from tools import split_cost` directly, without separately naming the billing module, since `__init__.py` code runs when the package itself is first imported and can expose inner names at the package level.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Nothing changes at all; `__init__`.py code technically never actually runs</t>
+          <t>Nothing changes at all; `__init__.py` code technically never actually runs</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>`main.py` can now write from tools import `split_cost` directly, skipping the billing name</t>
+          <t>`main.py` can now write `from tools import split_cost` directly, skipping the billing name</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A package is a folder containing related module files, plus a special file named `__init__`.py inside it; the mere presence of `__init__`.py is what tells Python to treat the folder as an importable package rather than an ordinary one.</t>
+          <t>A package is a folder containing related module files, plus a special file named `__init__.py` inside it; the mere presence of `__init__.py` is what tells Python to treat the folder as an importable package rather than an ordinary one.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>A folder of related modules plus an `__init__`.py file inside it</t>
+          <t>A folder of related modules plus an `__init__.py` file inside it</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Inside an online bookstore project's `tools/__init__`.py file, a developer sees a relative import: from .billing import `split_cost`. What does the leading dot in from .billing import `split_cost` mean?</t>
+          <t>Inside an online bookstore project's `tools/__init__.py` file, a developer sees a relative import: `from .billing import split_cost`. What does the leading dot in `from .billing import split_cost` mean?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
